--- a/tabla_ventanas_colecta.xlsx
+++ b/tabla_ventanas_colecta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\IA\01 Optimización de cargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DA8652-469D-4C99-A904-0CC510419D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14A1044-A8C8-4E31-84F9-D8B50225D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,27 @@
     <sheet name="Ventanas de Colecta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ventanas de Colecta'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ventanas de Colecta'!$A$1:$G$48</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="71">
   <si>
     <t>DUNS</t>
   </si>
@@ -311,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -327,6 +340,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,7 +652,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -680,8 +699,8 @@
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
+      <c r="E2" s="6">
+        <v>0.375</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -696,13 +715,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.41666666666666669</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -710,46 +729,46 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5"/>
+      <c r="D4" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5"/>
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -759,7 +778,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>15</v>
@@ -768,116 +787,116 @@
         <v>16</v>
       </c>
       <c r="F6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F11" s="4">
         <v>2</v>
       </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -887,7 +906,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -896,7 +915,7 @@
         <v>31</v>
       </c>
       <c r="F12" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -908,7 +927,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -917,179 +936,179 @@
         <v>31</v>
       </c>
       <c r="F13" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5"/>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F21" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1099,7 +1118,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>27</v>
@@ -1108,168 +1127,168 @@
         <v>28</v>
       </c>
       <c r="F22" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3"/>
+      <c r="A23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="4">
-        <v>2</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="4">
-        <v>2</v>
-      </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3"/>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>15</v>
@@ -1278,30 +1297,30 @@
         <v>16</v>
       </c>
       <c r="F30" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="A31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="4">
-        <v>2</v>
-      </c>
-      <c r="G31" s="5"/>
+      <c r="D31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1311,149 +1330,359 @@
         <v>59</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.33333333333333331</v>
       </c>
       <c r="F32" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="A33" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>23</v>
+      <c r="D34" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.41666666666666669</v>
       </c>
       <c r="F34" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.41666666666666669</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F35" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="A36" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="D36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F36" s="4">
+        <v>5</v>
+      </c>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.375</v>
       </c>
       <c r="F37" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F38" s="4">
+        <v>7</v>
+      </c>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="4">
+        <v>8</v>
+      </c>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="F40" s="4">
+        <v>9</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F41" s="4">
+        <v>10</v>
+      </c>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="4">
+        <v>11</v>
+      </c>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2</v>
+      </c>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5"/>
+    </row>
+    <row r="48" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F48" s="4">
         <v>2</v>
       </c>
-      <c r="G38" s="5"/>
+      <c r="G48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G48" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>